--- a/Stats Sheet/Round Gaps/Mythical.xlsx
+++ b/Stats Sheet/Round Gaps/Mythical.xlsx
@@ -70,6 +70,9 @@
     <x:t>18</x:t>
   </x:si>
   <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
     <x:t>Andrew512</x:t>
   </x:si>
   <x:si>
@@ -139,6 +142,9 @@
     <x:t>ERHDude</x:t>
   </x:si>
   <x:si>
+    <x:t>204</x:t>
+  </x:si>
+  <x:si>
     <x:t>FrostBros</x:t>
   </x:si>
   <x:si>
@@ -373,6 +379,9 @@
     <x:t>aalaan</x:t>
   </x:si>
   <x:si>
+    <x:t>395</x:t>
+  </x:si>
+  <x:si>
     <x:t>Bacan</x:t>
   </x:si>
   <x:si>
@@ -661,6 +670,9 @@
     <x:t>_Dieter</x:t>
   </x:si>
   <x:si>
+    <x:t>432</x:t>
+  </x:si>
+  <x:si>
     <x:t>Aybel</x:t>
   </x:si>
   <x:si>
@@ -701,6 +713,15 @@
   </x:si>
   <x:si>
     <x:t>SpaceFenix</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boomblade60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plushy33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YellowVitt</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1059,10 +1080,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V155"/>
+  <x:dimension ref="A1:W158"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:22" s="1" customFormat="1">
+    <x:row r="1" spans="1:23" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>43593</x:v>
       </x:c>
@@ -1117,8 +1138,11 @@
       <x:c r="V1" s="1">
         <x:v>46023</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:22">
+      <x:c r="W1" s="1">
+        <x:v>46114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:23">
       <x:c r="F2" s="0">
         <x:v>96</x:v>
       </x:c>
@@ -1170,8 +1194,11 @@
       <x:c r="V2" s="0">
         <x:v>113</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:22">
+      <x:c r="W2" s="0">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:23">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1226,13 +1253,16 @@
       <x:c r="V3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:22">
+      <x:c r="W3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:23">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
@@ -1241,18 +1271,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:22">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:23">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>0</x:v>
@@ -1261,27 +1291,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:23">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>0</x:v>
@@ -1290,101 +1320,104 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:23">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:23">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
@@ -1393,42 +1426,42 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="Q8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V8" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:22">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:23">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
@@ -1437,18 +1470,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:23">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
@@ -1457,15 +1490,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:23">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
@@ -1474,21 +1507,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:22">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:23">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
@@ -1497,98 +1530,101 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U12" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:22">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:23">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U13" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W13" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:23">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
@@ -1597,77 +1633,80 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V14" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:23">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V15" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:22">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="W15" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:23">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
@@ -1676,21 +1715,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:22">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:23">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
@@ -1699,119 +1738,122 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V17" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:23">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V18" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W18" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:23">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>0</x:v>
@@ -1820,21 +1862,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S19" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:22">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:23">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>0</x:v>
@@ -1843,65 +1885,68 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:23">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q21" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="R21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U21" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="V21" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W21" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:23">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>0</x:v>
@@ -1910,30 +1955,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:23">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>0</x:v>
@@ -1942,36 +1987,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q23" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:22">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:23">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>0</x:v>
@@ -1980,27 +2025,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O24" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="P24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R24" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:22">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:23">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>0</x:v>
@@ -2009,21 +2054,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:22">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:23">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>0</x:v>
@@ -2032,24 +2077,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:23">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>0</x:v>
@@ -2058,27 +2103,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L27" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:22">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:23">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>0</x:v>
@@ -2087,36 +2132,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L28" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:23">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>1</x:v>
@@ -2125,30 +2170,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M29" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O29" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:23">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>1</x:v>
@@ -2157,77 +2202,80 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:23">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O31" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="P31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U31" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="V31" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W31" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:23">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>1</x:v>
@@ -2236,54 +2284,54 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U32" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:23">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>1</x:v>
@@ -2292,24 +2340,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O33" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="T33" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="U33" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:23">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>1</x:v>
@@ -2318,24 +2366,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:23">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>1</x:v>
@@ -2344,15 +2392,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:23">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>1</x:v>
@@ -2361,39 +2409,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P36" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:23">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>1</x:v>
@@ -2402,21 +2450,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:22">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:23">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>1</x:v>
@@ -2425,24 +2473,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M38" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="N38" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:23">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>1</x:v>
@@ -2451,15 +2499,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:23">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>1</x:v>
@@ -2468,18 +2516,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:22">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:23">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>1</x:v>
@@ -2488,15 +2536,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:23">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>1</x:v>
@@ -2505,15 +2553,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:23">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>2</x:v>
@@ -2522,36 +2570,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="Q43" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="R43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S43" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:23">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>2</x:v>
@@ -2560,42 +2608,42 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I44" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L44" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="N44" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="P44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R44" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U44" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:23">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>2</x:v>
@@ -2604,121 +2652,127 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S45" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="T45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V45" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:23">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P46" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="V46" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:22">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="W46" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:23">
       <x:c r="A47" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L47" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V47" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:22">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="W47" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:23">
       <x:c r="A48" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>2</x:v>
@@ -2727,18 +2781,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N48" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:22">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:23">
       <x:c r="A49" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>2</x:v>
@@ -2747,27 +2801,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P49" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="R49" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:22">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:23">
       <x:c r="A50" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>2</x:v>
@@ -2776,15 +2830,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:23">
       <x:c r="A51" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>2</x:v>
@@ -2793,83 +2847,86 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L51" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:23">
       <x:c r="A52" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V52" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W52" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:23">
       <x:c r="A53" s="0">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>3</x:v>
@@ -2878,18 +2935,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I53" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:23">
       <x:c r="A54" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>3</x:v>
@@ -2898,47 +2955,50 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R54" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:22">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:23">
       <x:c r="A55" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T55" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="U55" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W55" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:23">
       <x:c r="A56" s="0">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>3</x:v>
@@ -2947,107 +3007,110 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T56" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:23">
       <x:c r="A57" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V57" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:22">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="W57" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:23">
       <x:c r="A58" s="0">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>3</x:v>
@@ -3056,18 +3119,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J58" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:22">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:23">
       <x:c r="A59" s="0">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>3</x:v>
@@ -3076,65 +3139,68 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H59" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I59" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:23">
       <x:c r="A60" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D60" s="0">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q60" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T60" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W60" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:23">
       <x:c r="A61" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>4</x:v>
@@ -3143,30 +3209,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L61" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q61" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:22">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:23">
       <x:c r="A62" s="0">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>4</x:v>
@@ -3175,15 +3241,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:23">
       <x:c r="A63" s="0">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>4</x:v>
@@ -3192,15 +3258,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:23">
       <x:c r="A64" s="0">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>4</x:v>
@@ -3209,15 +3275,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:23">
       <x:c r="A65" s="0">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>4</x:v>
@@ -3226,15 +3292,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I65" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:23">
       <x:c r="A66" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>4</x:v>
@@ -3243,15 +3309,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I66" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:23">
       <x:c r="A67" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>4</x:v>
@@ -3260,15 +3326,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I67" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:23">
       <x:c r="A68" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>4</x:v>
@@ -3277,27 +3343,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N68" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="P68" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R68" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V68" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:22">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:23">
       <x:c r="A69" s="0">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>4</x:v>
@@ -3306,15 +3372,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I69" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:23">
       <x:c r="A70" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>4</x:v>
@@ -3323,18 +3389,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I70" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N70" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:22">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:23">
       <x:c r="A71" s="0">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>4</x:v>
@@ -3343,15 +3409,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:23">
       <x:c r="A72" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>4</x:v>
@@ -3360,15 +3426,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I72" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:23">
       <x:c r="A73" s="0">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>4</x:v>
@@ -3377,33 +3443,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="I73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="Q73" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="R73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V73" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:22">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:23">
       <x:c r="A74" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>4</x:v>
@@ -3412,18 +3478,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:23">
       <x:c r="A75" s="0">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>4</x:v>
@@ -3432,15 +3498,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:23">
       <x:c r="A76" s="0">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>4</x:v>
@@ -3449,15 +3515,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I76" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:23">
       <x:c r="A77" s="0">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>4</x:v>
@@ -3466,15 +3532,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I77" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:23">
       <x:c r="A78" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>4</x:v>
@@ -3483,15 +3549,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I78" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:23">
       <x:c r="A79" s="0">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>4</x:v>
@@ -3500,33 +3566,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="I79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N79" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="T79" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="U79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V79" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:23">
       <x:c r="A80" s="0">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>4</x:v>
@@ -3535,15 +3601,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I80" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:23">
       <x:c r="A81" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>4</x:v>
@@ -3552,24 +3618,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I81" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T81" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="U81" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V81" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:23">
       <x:c r="A82" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>4</x:v>
@@ -3578,15 +3644,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I82" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:23">
       <x:c r="A83" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>4</x:v>
@@ -3595,15 +3661,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I83" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:23">
       <x:c r="A84" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>4</x:v>
@@ -3612,15 +3678,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I84" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:23">
       <x:c r="A85" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>4</x:v>
@@ -3629,15 +3695,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I85" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:23">
       <x:c r="A86" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>4</x:v>
@@ -3646,15 +3712,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I86" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:23">
       <x:c r="A87" s="0">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>4</x:v>
@@ -3663,24 +3729,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I87" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N87" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="Q87" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="U87" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:22">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:23">
       <x:c r="A88" s="0">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>4</x:v>
@@ -3689,15 +3755,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I88" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:23">
       <x:c r="A89" s="0">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>4</x:v>
@@ -3706,91 +3772,97 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I89" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:23">
       <x:c r="A90" s="0">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D90" s="0">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L90" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N90" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="O90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U90" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W90" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:23">
       <x:c r="A91" s="0">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I91" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q91" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="R91" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S91" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T91" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U91" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W91" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:23">
       <x:c r="A92" s="0">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>4</x:v>
@@ -3799,15 +3871,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I92" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:23">
       <x:c r="A93" s="0">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>4</x:v>
@@ -3816,30 +3888,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I93" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M93" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="N93" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O93" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S93" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U93" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:22">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:23">
       <x:c r="A94" s="0">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>4</x:v>
@@ -3848,15 +3920,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I94" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:23">
       <x:c r="A95" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>4</x:v>
@@ -3865,15 +3937,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I95" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:23">
       <x:c r="A96" s="0">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>4</x:v>
@@ -3882,15 +3954,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I96" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:23">
       <x:c r="A97" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>4</x:v>
@@ -3899,27 +3971,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I97" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O97" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="Q97" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S97" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T97" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:23">
       <x:c r="A98" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>4</x:v>
@@ -3928,15 +4000,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I98" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:23">
       <x:c r="A99" s="0">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>4</x:v>
@@ -3945,15 +4017,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I99" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:23">
       <x:c r="A100" s="0">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>4</x:v>
@@ -3962,15 +4034,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I100" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:23">
       <x:c r="A101" s="0">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>4</x:v>
@@ -3979,15 +4051,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I101" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:23">
       <x:c r="A102" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>4</x:v>
@@ -3996,15 +4068,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I102" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:23">
       <x:c r="A103" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>4</x:v>
@@ -4013,27 +4085,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I103" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N103" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="O103" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q103" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S103" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:22">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:23">
       <x:c r="A104" s="0">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>4</x:v>
@@ -4042,15 +4114,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I104" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:23">
       <x:c r="A105" s="0">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>4</x:v>
@@ -4059,15 +4131,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I105" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:23">
       <x:c r="A106" s="0">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>4</x:v>
@@ -4076,15 +4148,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I106" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:23">
       <x:c r="A107" s="0">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>4</x:v>
@@ -4093,18 +4165,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I107" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:23">
       <x:c r="A108" s="0">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>4</x:v>
@@ -4113,15 +4185,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I108" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:23">
       <x:c r="A109" s="0">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>5</x:v>
@@ -4130,68 +4202,71 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J109" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M109" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="N109" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:23">
       <x:c r="A110" s="0">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T110" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U110" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W110" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:23">
       <x:c r="A111" s="0">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>6</x:v>
@@ -4200,65 +4275,68 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:23">
       <x:c r="A112" s="0">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D112" s="0">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V112" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W112" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:23">
       <x:c r="A113" s="0">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>6</x:v>
@@ -4267,18 +4345,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L113" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:23">
       <x:c r="A114" s="0">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>6</x:v>
@@ -4287,15 +4365,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:23">
       <x:c r="A115" s="0">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>6</x:v>
@@ -4304,27 +4382,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L115" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M115" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O115" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="U115" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:22">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:23">
       <x:c r="A116" s="0">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>7</x:v>
@@ -4333,21 +4411,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="L116" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N116" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="R116" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:22">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:23">
       <x:c r="A117" s="0">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>7</x:v>
@@ -4356,24 +4434,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L117" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q117" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="R117" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T117" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:22">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:23">
       <x:c r="A118" s="0">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>7</x:v>
@@ -4382,18 +4460,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L118" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N118" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:22">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:23">
       <x:c r="A119" s="0">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>7</x:v>
@@ -4402,85 +4480,91 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L119" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:23">
       <x:c r="A120" s="0">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D120" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L120" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M120" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N120" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O120" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P120" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q120" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S120" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T120" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W120" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:23">
       <x:c r="A121" s="0">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L121" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O121" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="P121" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R121" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T121" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U121" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W121" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:23">
       <x:c r="A122" s="0">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>7</x:v>
@@ -4489,47 +4573,50 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L122" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N122" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="O122" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P122" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T122" s="0" t="s">
-        <x:v>193</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:22">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:23">
       <x:c r="A123" s="0">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M123" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U123" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:22">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="W123" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:23">
       <x:c r="A124" s="0">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>8</x:v>
@@ -4538,21 +4625,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M124" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N124" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O124" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:23">
       <x:c r="A125" s="0">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>8</x:v>
@@ -4561,15 +4648,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M125" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:23">
       <x:c r="A126" s="0">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>8</x:v>
@@ -4578,27 +4665,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="M126" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N126" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q126" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="T126" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="U126" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:23">
       <x:c r="A127" s="0">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>8</x:v>
@@ -4607,18 +4694,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M127" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N127" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:23">
       <x:c r="A128" s="0">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>8</x:v>
@@ -4627,82 +4714,88 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M128" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N128" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:23">
       <x:c r="A129" s="0">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M129" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N129" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R129" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T129" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" spans="1:22">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="W129" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:23">
       <x:c r="A130" s="0">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="N130" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O130" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q130" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R130" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S130" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T130" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U130" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V130" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W130" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:23">
       <x:c r="A131" s="0">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>9</x:v>
@@ -4711,15 +4804,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N131" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:23">
       <x:c r="A132" s="0">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>9</x:v>
@@ -4728,33 +4821,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="N132" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O132" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P132" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q132" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S132" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T132" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U132" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:23">
       <x:c r="A133" s="0">
         <x:v>130</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>9</x:v>
@@ -4763,44 +4856,47 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N133" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:23">
       <x:c r="A134" s="0">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N134" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O134" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P134" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R134" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V134" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" spans="1:22">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="W134" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:23">
       <x:c r="A135" s="0">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>9</x:v>
@@ -4809,15 +4905,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N135" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:23">
       <x:c r="A136" s="0">
         <x:v>133</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>9</x:v>
@@ -4826,24 +4922,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N136" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O136" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q136" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R136" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:23">
       <x:c r="A137" s="0">
         <x:v>134</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>10</x:v>
@@ -4852,18 +4948,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="O137" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P137" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:23">
       <x:c r="A138" s="0">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>10</x:v>
@@ -4872,24 +4968,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="O138" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q138" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="T138" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="U138" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:23">
       <x:c r="A139" s="0">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>11</x:v>
@@ -4898,73 +4994,79 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P139" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q139" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R139" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V139" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140" spans="1:22">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:23">
       <x:c r="A140" s="0">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D140" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="Q140" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R140" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S140" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T140" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U140" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="141" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W140" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:23">
       <x:c r="A141" s="0">
         <x:v>138</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Q141" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S141" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="142" spans="1:22">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="W141" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:23">
       <x:c r="A142" s="0">
         <x:v>139</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
         <x:v>12</x:v>
@@ -4973,82 +5075,88 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q142" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S142" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T142" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U142" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V142" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:23">
       <x:c r="A143" s="0">
         <x:v>140</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="Q143" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R143" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S143" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T143" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U143" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V143" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W143" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:23">
       <x:c r="A144" s="0">
         <x:v>141</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D144" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q144" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T144" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="V144" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:22">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="W144" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:23">
       <x:c r="A145" s="0">
         <x:v>142</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
         <x:v>12</x:v>
@@ -5057,15 +5165,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q145" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:23">
       <x:c r="A146" s="0">
         <x:v>143</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>12</x:v>
@@ -5074,47 +5182,50 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q146" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S146" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T146" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:23">
       <x:c r="A147" s="0">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D147" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q147" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R147" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S147" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U147" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" spans="1:22">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="W147" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:23">
       <x:c r="A148" s="0">
         <x:v>145</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>12</x:v>
@@ -5123,24 +5234,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Q148" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S148" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T148" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U148" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:23">
       <x:c r="A149" s="0">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>14</x:v>
@@ -5149,18 +5260,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S149" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T149" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:23">
       <x:c r="A150" s="0">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>14</x:v>
@@ -5169,38 +5280,41 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S150" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:23">
       <x:c r="A151" s="0">
         <x:v>148</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D151" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T151" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U151" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V151" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W151" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:23">
       <x:c r="A152" s="0">
         <x:v>149</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
         <x:v>15</x:v>
@@ -5209,35 +5323,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="T152" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V152" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" spans="1:22">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:23">
       <x:c r="A153" s="0">
         <x:v>150</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D153" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V153" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W153" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:23">
       <x:c r="A154" s="0">
         <x:v>151</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
         <x:v>17</x:v>
@@ -5246,24 +5363,78 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V154" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:23">
       <x:c r="A155" s="0">
         <x:v>152</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D155" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V155" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W155" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:23">
+      <x:c r="A156" s="0">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D156" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W156" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:23">
+      <x:c r="A157" s="0">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D157" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W157" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:23">
+      <x:c r="A158" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D158" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W158" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
